--- a/extra_files/params_sample.xlsx
+++ b/extra_files/params_sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Economics-Notebook\intermacro\shinyapp\Long Run\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\econ\The-Solow-Growth-Model\extra_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918673E9-53A5-4661-9915-D7024075F077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F2353D8-40C1-48B3-B263-3435C2F0294B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3960" yWindow="-20820" windowWidth="28800" windowHeight="15345" xr2:uid="{B013E5D7-4F34-47C8-AD29-D93E5012CD83}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B013E5D7-4F34-47C8-AD29-D93E5012CD83}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>param</t>
   </si>
@@ -51,6 +51,48 @@
   </si>
   <si>
     <t>value</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>The shiny app will only upload content in the required columns</t>
+  </si>
+  <si>
+    <t>Exogenous Variable options: s, delta, n, z, l</t>
+  </si>
+  <si>
+    <t>Endogenous Variable options: A, L, Y, K, little_k</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>For first set of quantitative experiments</t>
+  </si>
+  <si>
+    <t>For second set of quantitative experients</t>
+  </si>
+  <si>
+    <t>extra</t>
+  </si>
+  <si>
+    <t>Making endogenous edits overwrites the calculation for that endoegnous variable. When overwriting endogenous variables, keep in mind the order of the calculations as other endogenous variables can depend on the result of the new endo value. Unchaged endo variables will run calculations as normal so it will use the determined exogenous variables and when applicable use the calculated/overwritten endogenous values.</t>
+  </si>
+  <si>
+    <t>param: only one parameter</t>
+  </si>
+  <si>
+    <t>Do not mix exogenous and endogenous variables</t>
+  </si>
+  <si>
+    <t>value: any numeric value</t>
+  </si>
+  <si>
+    <t>It is assume proper values will be use.</t>
+  </si>
+  <si>
+    <t>Using unreasonable numbers for the target variable can results in errors (eg. 0, negative numbers or large numbers).  For example a savings rate greater than 1. A country cannot save 100% or more of their income as it is not realistic. Some calculations divide or subtract by the savings rate so a value of 1 can result in zero when subtracting or get a div by zero error when dividing. I guess in some extreme cases a country can have a negative savings or savings greater than 100%, and in that case this model is not set up to deal with such scenario according to my understanding of the model.</t>
   </si>
 </sst>
 </file>
@@ -422,10 +464,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D1D3DDC-9F00-4C24-AA92-F3C472B9B219}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="57.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -438,8 +487,17 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -451,6 +509,47 @@
       </c>
       <c r="D2">
         <v>200</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
